--- a/excel/kpi_reconciliation.xlsx
+++ b/excel/kpi_reconciliation.xlsx
@@ -12,7 +12,7 @@
     <sheet name="HHI &amp; Concentration" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +149,7 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -519,20 +520,20 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="61" customWidth="1" min="1" max="1"/>
+    <col width="63" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="73" customWidth="1" min="3" max="3"/>
+    <col width="77" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CREDITLENS — FINANCIAL KPI RECONCILIATION &amp; AUDIT WORKBOOK</t>
+          <t>CREDITLENS â€” FINANCIAL KPI RECONCILIATION &amp; AUDIT WORKBOOK</t>
         </is>
       </c>
     </row>
@@ -546,7 +547,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>CreditLens — Indian Banking &amp; Credit Portfolio Analytics</t>
+          <t>CreditLens â€” Indian Banking &amp; Credit Portfolio Analytics</t>
         </is>
       </c>
     </row>
@@ -558,7 +559,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Reserve Bank of India (RBI) — DBIE Table 16</t>
+          <t>Reserve Bank of India (RBI) â€” DBIE Table 16</t>
         </is>
       </c>
     </row>
@@ -582,7 +583,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Rupees crore (₹ Cr)</t>
+          <t>Rupees crore (â‚¹ Cr)</t>
         </is>
       </c>
     </row>
@@ -606,7 +607,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Python Pipeline vs SQLite/PostgreSQL Views vs Excel Dynamic Formulas</t>
+          <t>Independent pandas and SQLite calculations with Excel formula checks</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>100% RECONCILED — Zero Discrepancies across all representative periods</t>
+          <t>Formula checks recalculate when opened in Excel; inspect comparison status</t>
         </is>
       </c>
     </row>
@@ -711,7 +712,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -723,7 +724,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>MoM Credit Change (₹ Cr)</t>
+          <t>MoM Credit Change (â‚¹ Cr)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -747,7 +748,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -783,7 +784,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -795,7 +796,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>YoY Credit Change (₹ Cr)</t>
+          <t>YoY Credit Change (â‚¹ Cr)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -819,7 +820,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -855,7 +856,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -891,7 +892,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -927,7 +928,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -963,7 +964,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>RECONCILED</t>
+          <t>SPECIFIED</t>
         </is>
       </c>
     </row>
@@ -981,20 +982,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="103" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1023,7 +1026,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Credit Outstanding (₹ Cr)</t>
+          <t>Credit Outstanding (â‚¹ Cr)</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -1059,6 +1062,16 @@
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Reconciliation Audit</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Prior Year Credit</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>Grand Total Credit</t>
         </is>
       </c>
     </row>
@@ -1082,27 +1095,34 @@
         <v>1511787.18</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>10.89</v>
+        <v>10.88522498544757</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>10.89</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>10.89</v>
+      <c r="G4" s="11">
+        <f>IFERROR((D4-L4)/L4*100,"")</f>
+        <v/>
       </c>
       <c r="H4" s="12" t="n">
-        <v>31.6836</v>
+        <v>31.68360109567005</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>31.6836</v>
       </c>
-      <c r="J4" s="12" t="n">
-        <v>31.6836</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J4" s="12">
+        <f>IFERROR(D4/M4*100,"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="7">
+        <f>IF(AND(ABS(E4-F4)&lt;0.01,ABS(E4-G4)&lt;0.01,ABS(H4-I4)&lt;0.01,ABS(H4-J4)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>1363380.18</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="5">
@@ -1125,27 +1145,34 @@
         <v>534392.02</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>20.89</v>
+        <v>20.88816485609581</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>20.89</v>
       </c>
-      <c r="G5" s="11" t="n">
-        <v>20.89</v>
+      <c r="G5" s="11">
+        <f>IFERROR((D5-L5)/L5*100,"")</f>
+        <v/>
       </c>
       <c r="H5" s="12" t="n">
-        <v>11.1996</v>
+        <v>11.19963432312565</v>
       </c>
       <c r="I5" s="12" t="n">
         <v>11.1996</v>
       </c>
-      <c r="J5" s="12" t="n">
-        <v>11.1996</v>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J5" s="12">
+        <f>IFERROR(D5/M5*100,"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="7">
+        <f>IF(AND(ABS(E5-F5)&lt;0.01,ABS(E5-G5)&lt;0.01,ABS(H5-I5)&lt;0.01,ABS(H5-J5)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>442054.87</v>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="6">
@@ -1168,27 +1195,34 @@
         <v>374052.04</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>29.23</v>
+        <v>29.22876500192502</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>29.23</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>29.23</v>
+      <c r="G6" s="11">
+        <f>IFERROR((D6-L6)/L6*100,"")</f>
+        <v/>
       </c>
       <c r="H6" s="12" t="n">
-        <v>7.8393</v>
+        <v>7.83927511832824</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>7.8393</v>
       </c>
-      <c r="J6" s="12" t="n">
-        <v>7.8393</v>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J6" s="12">
+        <f>IFERROR(D6/M6*100,"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="7">
+        <f>IF(AND(ABS(E6-F6)&lt;0.01,ABS(E6-G6)&lt;0.01,ABS(H6-I6)&lt;0.01,ABS(H6-J6)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>289449.52</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="7">
@@ -1211,27 +1245,34 @@
         <v>342309.11</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>37.59</v>
+        <v>37.59464354248502</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>37.59</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>37.59</v>
+      <c r="G7" s="11">
+        <f>IFERROR((D7-L7)/L7*100,"")</f>
+        <v/>
       </c>
       <c r="H7" s="12" t="n">
-        <v>7.174</v>
+        <v>7.174015917143733</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>7.174</v>
       </c>
-      <c r="J7" s="12" t="n">
-        <v>7.174</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J7" s="12">
+        <f>IFERROR(D7/M7*100,"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="7">
+        <f>IF(AND(ABS(E7-F7)&lt;0.01,ABS(E7-G7)&lt;0.01,ABS(H7-I7)&lt;0.01,ABS(H7-J7)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>248780.84</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="8">
@@ -1254,27 +1295,34 @@
         <v>328675.04</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>21.26</v>
+        <v>21.2577691384433</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>21.26</v>
       </c>
-      <c r="G8" s="11" t="n">
-        <v>21.26</v>
+      <c r="G8" s="11">
+        <f>IFERROR((D8-L8)/L8*100,"")</f>
+        <v/>
       </c>
       <c r="H8" s="12" t="n">
-        <v>6.8883</v>
+        <v>6.888276997734162</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>6.8883</v>
       </c>
-      <c r="J8" s="12" t="n">
-        <v>6.8883</v>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J8" s="12">
+        <f>IFERROR(D8/M8*100,"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>IF(AND(ABS(E8-F8)&lt;0.01,ABS(E8-G8)&lt;0.01,ABS(H8-I8)&lt;0.01,ABS(H8-J8)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>271054.83</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="9">
@@ -1297,27 +1345,34 @@
         <v>309020.45</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>11.45</v>
+        <v>11.44680988569489</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>11.45</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>11.45</v>
+      <c r="G9" s="11">
+        <f>IFERROR((D9-L9)/L9*100,"")</f>
+        <v/>
       </c>
       <c r="H9" s="12" t="n">
-        <v>6.4764</v>
+        <v>6.476361751000198</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>6.4764</v>
       </c>
-      <c r="J9" s="12" t="n">
-        <v>6.4764</v>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J9" s="12">
+        <f>IFERROR(D9/M9*100,"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="7">
+        <f>IF(AND(ABS(E9-F9)&lt;0.01,ABS(E9-G9)&lt;0.01,ABS(H9-I9)&lt;0.01,ABS(H9-J9)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>277280.66</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="10">
@@ -1340,27 +1395,34 @@
         <v>266733.24</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>19.54</v>
+        <v>19.53943390992232</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>19.54</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <v>19.54</v>
+      <c r="G10" s="11">
+        <f>IFERROR((D10-L10)/L10*100,"")</f>
+        <v/>
       </c>
       <c r="H10" s="12" t="n">
-        <v>5.5901</v>
+        <v>5.590118560944286</v>
       </c>
       <c r="I10" s="12" t="n">
         <v>5.5901</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>5.5901</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J10" s="12">
+        <f>IFERROR(D10/M10*100,"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="7">
+        <f>IF(AND(ABS(E10-F10)&lt;0.01,ABS(E10-G10)&lt;0.01,ABS(H10-I10)&lt;0.01,ABS(H10-J10)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>223134.1</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="11">
@@ -1383,27 +1445,34 @@
         <v>229656</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>48.55</v>
+        <v>48.54623509329127</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>48.55</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>48.55</v>
+      <c r="G11" s="11">
+        <f>IFERROR((D11-L11)/L11*100,"")</f>
+        <v/>
       </c>
       <c r="H11" s="12" t="n">
-        <v>4.8131</v>
+        <v>4.813064424337293</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>4.8131</v>
       </c>
-      <c r="J11" s="12" t="n">
-        <v>4.8131</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J11" s="12">
+        <f>IFERROR(D11/M11*100,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="7">
+        <f>IF(AND(ABS(E11-F11)&lt;0.01,ABS(E11-G11)&lt;0.01,ABS(H11-I11)&lt;0.01,ABS(H11-J11)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>154602.37</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="12">
@@ -1426,27 +1495,34 @@
         <v>191165.8</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>19.27</v>
+        <v>19.27009614565135</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>19.27</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>19.27</v>
+      <c r="G12" s="11">
+        <f>IFERROR((D12-L12)/L12*100,"")</f>
+        <v/>
       </c>
       <c r="H12" s="12" t="n">
-        <v>4.0064</v>
+        <v>4.006397878261304</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>4.0064</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>4.0064</v>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J12" s="12">
+        <f>IFERROR(D12/M12*100,"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="7">
+        <f>IF(AND(ABS(E12-F12)&lt;0.01,ABS(E12-G12)&lt;0.01,ABS(H12-I12)&lt;0.01,ABS(H12-J12)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>160279.74</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="13">
@@ -1469,27 +1545,34 @@
         <v>153226</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>26.05</v>
+        <v>26.04622413303222</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>26.05</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>26.05</v>
+      <c r="G13" s="11">
+        <f>IFERROR((D13-L13)/L13*100,"")</f>
+        <v/>
       </c>
       <c r="H13" s="12" t="n">
-        <v>3.2113</v>
+        <v>3.211266457151157</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>3.2113</v>
       </c>
-      <c r="J13" s="12" t="n">
-        <v>3.2113</v>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J13" s="12">
+        <f>IFERROR(D13/M13*100,"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="7">
+        <f>IF(AND(ABS(E13-F13)&lt;0.01,ABS(E13-G13)&lt;0.01,ABS(H13-I13)&lt;0.01,ABS(H13-J13)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>121563.34</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="14">
@@ -1512,27 +1595,34 @@
         <v>117972.89</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>32.71</v>
+        <v>32.70697371168162</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>32.71</v>
       </c>
-      <c r="G14" s="11" t="n">
-        <v>32.71</v>
+      <c r="G14" s="11">
+        <f>IFERROR((D14-L14)/L14*100,"")</f>
+        <v/>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2.4724</v>
+        <v>2.472441912666148</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>2.4724</v>
       </c>
-      <c r="J14" s="12" t="n">
-        <v>2.4724</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J14" s="12">
+        <f>IFERROR(D14/M14*100,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="7">
+        <f>IF(AND(ABS(E14-F14)&lt;0.01,ABS(E14-G14)&lt;0.01,ABS(H14-I14)&lt;0.01,ABS(H14-J14)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>88897.28</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="15">
@@ -1555,27 +1645,34 @@
         <v>116125</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>13.17</v>
+        <v>13.17042574397434</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>13.17</v>
       </c>
-      <c r="G15" s="11" t="n">
-        <v>13.17</v>
+      <c r="G15" s="11">
+        <f>IFERROR((D15-L15)/L15*100,"")</f>
+        <v/>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2.4337</v>
+        <v>2.433714365294911</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>2.4337</v>
       </c>
-      <c r="J15" s="12" t="n">
-        <v>2.4337</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J15" s="12">
+        <f>IFERROR(D15/M15*100,"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="7">
+        <f>IF(AND(ABS(E15-F15)&lt;0.01,ABS(E15-G15)&lt;0.01,ABS(H15-I15)&lt;0.01,ABS(H15-J15)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>102610.73</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="16">
@@ -1598,27 +1695,34 @@
         <v>68921.95</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>16.46</v>
+        <v>16.45630384705522</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>16.46</v>
       </c>
-      <c r="G16" s="11" t="n">
-        <v>16.46</v>
+      <c r="G16" s="11">
+        <f>IFERROR((D16-L16)/L16*100,"")</f>
+        <v/>
       </c>
       <c r="H16" s="12" t="n">
-        <v>1.4444</v>
+        <v>1.44444641377083</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>1.4444</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>1.4444</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J16" s="12">
+        <f>IFERROR(D16/M16*100,"")</f>
+        <v/>
+      </c>
+      <c r="K16" s="7">
+        <f>IF(AND(ABS(E16-F16)&lt;0.01,ABS(E16-G16)&lt;0.01,ABS(H16-I16)&lt;0.01,ABS(H16-J16)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>59182.67</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="17">
@@ -1641,27 +1745,34 @@
         <v>64261.17</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>12.72</v>
+        <v>12.72180848376667</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>12.72</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>12.72</v>
+      <c r="G17" s="11">
+        <f>IFERROR((D17-L17)/L17*100,"")</f>
+        <v/>
       </c>
       <c r="H17" s="12" t="n">
-        <v>1.3468</v>
+        <v>1.346767126455616</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>1.3468</v>
       </c>
-      <c r="J17" s="12" t="n">
-        <v>1.3468</v>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J17" s="12">
+        <f>IFERROR(D17/M17*100,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="7">
+        <f>IF(AND(ABS(E17-F17)&lt;0.01,ABS(E17-G17)&lt;0.01,ABS(H17-I17)&lt;0.01,ABS(H17-J17)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>57008.64</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="18">
@@ -1684,27 +1795,34 @@
         <v>62076.48</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>17.72</v>
+        <v>17.72387104408865</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>17.72</v>
       </c>
-      <c r="G18" s="11" t="n">
-        <v>17.72</v>
+      <c r="G18" s="11">
+        <f>IFERROR((D18-L18)/L18*100,"")</f>
+        <v/>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1.301</v>
+        <v>1.300981021510805</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>1.301</v>
       </c>
-      <c r="J18" s="12" t="n">
-        <v>1.301</v>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J18" s="12">
+        <f>IFERROR(D18/M18*100,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="7">
+        <f>IF(AND(ABS(E18-F18)&lt;0.01,ABS(E18-G18)&lt;0.01,ABS(H18-I18)&lt;0.01,ABS(H18-J18)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>52730.58</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="19">
@@ -1727,27 +1845,34 @@
         <v>37681.31</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>8.789999999999999</v>
+        <v>8.786703770650485</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>8.789999999999999</v>
+      <c r="G19" s="11">
+        <f>IFERROR((D19-L19)/L19*100,"")</f>
+        <v/>
       </c>
       <c r="H19" s="12" t="n">
-        <v>0.7897</v>
+        <v>0.7897140620032791</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0.7897</v>
       </c>
-      <c r="J19" s="12" t="n">
-        <v>0.7897</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J19" s="12">
+        <f>IFERROR(D19/M19*100,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="7">
+        <f>IF(AND(ABS(E19-F19)&lt;0.01,ABS(E19-G19)&lt;0.01,ABS(H19-I19)&lt;0.01,ABS(H19-J19)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>34637.79</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="20">
@@ -1770,27 +1895,34 @@
         <v>32587.8</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>15.14</v>
+        <v>15.13907187897815</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>15.14</v>
       </c>
-      <c r="G20" s="11" t="n">
-        <v>15.14</v>
+      <c r="G20" s="11">
+        <f>IFERROR((D20-L20)/L20*100,"")</f>
+        <v/>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6829657437533478</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J20" s="12" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J20" s="12">
+        <f>IFERROR(D20/M20*100,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="7">
+        <f>IF(AND(ABS(E20-F20)&lt;0.01,ABS(E20-G20)&lt;0.01,ABS(H20-I20)&lt;0.01,ABS(H20-J20)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>28302.99</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="21">
@@ -1813,27 +1945,34 @@
         <v>16307.29</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>23.13</v>
+        <v>23.13494313784269</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>23.13</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>23.13</v>
+      <c r="G21" s="11">
+        <f>IFERROR((D21-L21)/L21*100,"")</f>
+        <v/>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0.3418</v>
+        <v>0.3417634956471911</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0.3418</v>
       </c>
-      <c r="J21" s="12" t="n">
-        <v>0.3418</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J21" s="12">
+        <f>IFERROR(D21/M21*100,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="7">
+        <f>IF(AND(ABS(E21-F21)&lt;0.01,ABS(E21-G21)&lt;0.01,ABS(H21-I21)&lt;0.01,ABS(H21-J21)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>13243.43</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="22">
@@ -1856,27 +1995,34 @@
         <v>14562.07</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>10.26</v>
+        <v>10.26149308881375</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>10.26</v>
       </c>
-      <c r="G22" s="11" t="n">
-        <v>10.26</v>
+      <c r="G22" s="11">
+        <f>IFERROR((D22-L22)/L22*100,"")</f>
+        <v/>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0.3052</v>
+        <v>0.3051876766194194</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0.3052</v>
       </c>
-      <c r="J22" s="12" t="n">
-        <v>0.3052</v>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J22" s="12">
+        <f>IFERROR(D22/M22*100,"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="7">
+        <f>IF(AND(ABS(E22-F22)&lt;0.01,ABS(E22-G22)&lt;0.01,ABS(H22-I22)&lt;0.01,ABS(H22-J22)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>13206.85</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>4771513.11</v>
       </c>
     </row>
     <row r="23">
@@ -1899,27 +2045,34 @@
         <v>1363380.18</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.84</v>
+        <v>0.8369492307128613</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0.84</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>0.84</v>
+      <c r="G23" s="11">
+        <f>IFERROR((D23-L23)/L23*100,"")</f>
+        <v/>
       </c>
       <c r="H23" s="12" t="n">
-        <v>34.0726</v>
+        <v>34.07256709093827</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>34.0726</v>
       </c>
-      <c r="J23" s="12" t="n">
-        <v>34.0726</v>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J23" s="12">
+        <f>IFERROR(D23/M23*100,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="7">
+        <f>IF(AND(ABS(E23-F23)&lt;0.01,ABS(E23-G23)&lt;0.01,ABS(H23-I23)&lt;0.01,ABS(H23-J23)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>1352064.09</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="24">
@@ -1942,27 +2095,34 @@
         <v>442054.87</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>11.02</v>
+        <v>11.01832074691691</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>11.02</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>11.02</v>
+      <c r="G24" s="11">
+        <f>IFERROR((D24-L24)/L24*100,"")</f>
+        <v/>
       </c>
       <c r="H24" s="12" t="n">
-        <v>11.0475</v>
+        <v>11.0475012303252</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>11.0475</v>
       </c>
-      <c r="J24" s="12" t="n">
-        <v>11.0475</v>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J24" s="12">
+        <f>IFERROR(D24/M24*100,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="7">
+        <f>IF(AND(ABS(E24-F24)&lt;0.01,ABS(E24-G24)&lt;0.01,ABS(H24-I24)&lt;0.01,ABS(H24-J24)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>398181.91</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="25">
@@ -1985,27 +2145,34 @@
         <v>289449.52</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>8.57</v>
+        <v>8.566693348599594</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>8.57</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>8.57</v>
+      <c r="G25" s="11">
+        <f>IFERROR((D25-L25)/L25*100,"")</f>
+        <v/>
       </c>
       <c r="H25" s="12" t="n">
-        <v>7.2337</v>
+        <v>7.233703653840617</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>7.2337</v>
       </c>
-      <c r="J25" s="12" t="n">
-        <v>7.2337</v>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J25" s="12">
+        <f>IFERROR(D25/M25*100,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="7">
+        <f>IF(AND(ABS(E25-F25)&lt;0.01,ABS(E25-G25)&lt;0.01,ABS(H25-I25)&lt;0.01,ABS(H25-J25)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>266609.87</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="26">
@@ -2028,27 +2195,34 @@
         <v>277280.66</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8.619999999999999</v>
+        <v>8.620544307972656</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="G26" s="11" t="n">
-        <v>8.619999999999999</v>
+      <c r="G26" s="11">
+        <f>IFERROR((D26-L26)/L26*100,"")</f>
+        <v/>
       </c>
       <c r="H26" s="12" t="n">
-        <v>6.9296</v>
+        <v>6.929588701274536</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>6.9296</v>
       </c>
-      <c r="J26" s="12" t="n">
-        <v>6.9296</v>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J26" s="12">
+        <f>IFERROR(D26/M26*100,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="7">
+        <f>IF(AND(ABS(E26-F26)&lt;0.01,ABS(E26-G26)&lt;0.01,ABS(H26-I26)&lt;0.01,ABS(H26-J26)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>255274.6</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="27">
@@ -2071,27 +2245,34 @@
         <v>271054.83</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>6.32</v>
+        <v>6.317016671764414</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>6.32</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>6.32</v>
+      <c r="G27" s="11">
+        <f>IFERROR((D27-L27)/L27*100,"")</f>
+        <v/>
       </c>
       <c r="H27" s="12" t="n">
-        <v>6.774</v>
+        <v>6.773997463053825</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>6.774</v>
       </c>
-      <c r="J27" s="12" t="n">
-        <v>6.774</v>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J27" s="12">
+        <f>IFERROR(D27/M27*100,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="7">
+        <f>IF(AND(ABS(E27-F27)&lt;0.01,ABS(E27-G27)&lt;0.01,ABS(H27-I27)&lt;0.01,ABS(H27-J27)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>254949.62</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="28">
@@ -2114,27 +2295,34 @@
         <v>248780.84</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>22.11</v>
+        <v>22.10672507953623</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>22.11</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>22.11</v>
+      <c r="G28" s="11">
+        <f>IFERROR((D28-L28)/L28*100,"")</f>
+        <v/>
       </c>
       <c r="H28" s="12" t="n">
-        <v>6.2173</v>
+        <v>6.217342738428234</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>6.2173</v>
       </c>
-      <c r="J28" s="12" t="n">
-        <v>6.2173</v>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J28" s="12">
+        <f>IFERROR(D28/M28*100,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="7">
+        <f>IF(AND(ABS(E28-F28)&lt;0.01,ABS(E28-G28)&lt;0.01,ABS(H28-I28)&lt;0.01,ABS(H28-J28)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>203740.49</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="29">
@@ -2157,27 +2345,34 @@
         <v>223134.1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>8.1</v>
+        <v>8.103165141277138</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>8.1</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>8.1</v>
+      <c r="G29" s="11">
+        <f>IFERROR((D29-L29)/L29*100,"")</f>
+        <v/>
       </c>
       <c r="H29" s="12" t="n">
-        <v>5.5764</v>
+        <v>5.576398794741266</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>5.5764</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <v>5.5764</v>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J29" s="12">
+        <f>IFERROR(D29/M29*100,"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="7">
+        <f>IF(AND(ABS(E29-F29)&lt;0.01,ABS(E29-G29)&lt;0.01,ABS(H29-I29)&lt;0.01,ABS(H29-J29)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>206408.48</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="30">
@@ -2200,27 +2395,34 @@
         <v>160279.74</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>10.28</v>
+        <v>10.27600971377177</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>10.28</v>
       </c>
-      <c r="G30" s="11" t="n">
-        <v>10.28</v>
+      <c r="G30" s="11">
+        <f>IFERROR((D30-L30)/L30*100,"")</f>
+        <v/>
       </c>
       <c r="H30" s="12" t="n">
-        <v>4.0056</v>
+        <v>4.005590131483459</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>4.0056</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>4.0056</v>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J30" s="12">
+        <f>IFERROR(D30/M30*100,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="7">
+        <f>IF(AND(ABS(E30-F30)&lt;0.01,ABS(E30-G30)&lt;0.01,ABS(H30-I30)&lt;0.01,ABS(H30-J30)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>145344.16</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="31">
@@ -2243,27 +2445,34 @@
         <v>154602.37</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3.03</v>
+        <v>3.030908265511252</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>3.03</v>
       </c>
-      <c r="G31" s="11" t="n">
-        <v>3.03</v>
+      <c r="G31" s="11">
+        <f>IFERROR((D31-L31)/L31*100,"")</f>
+        <v/>
       </c>
       <c r="H31" s="12" t="n">
-        <v>3.8637</v>
+        <v>3.863705591086899</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>3.8637</v>
       </c>
-      <c r="J31" s="12" t="n">
-        <v>3.8637</v>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J31" s="12">
+        <f>IFERROR(D31/M31*100,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="7">
+        <f>IF(AND(ABS(E31-F31)&lt;0.01,ABS(E31-G31)&lt;0.01,ABS(H31-I31)&lt;0.01,ABS(H31-J31)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>150054.36</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="32">
@@ -2286,27 +2495,34 @@
         <v>121563.34</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>7.1</v>
+        <v>7.095602311636824</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>7.1</v>
       </c>
-      <c r="G32" s="11" t="n">
-        <v>7.1</v>
+      <c r="G32" s="11">
+        <f>IFERROR((D32-L32)/L32*100,"")</f>
+        <v/>
       </c>
       <c r="H32" s="12" t="n">
-        <v>3.038</v>
+        <v>3.038019122405417</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>3.038</v>
       </c>
-      <c r="J32" s="12" t="n">
-        <v>3.038</v>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J32" s="12">
+        <f>IFERROR(D32/M32*100,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="7">
+        <f>IF(AND(ABS(E32-F32)&lt;0.01,ABS(E32-G32)&lt;0.01,ABS(H32-I32)&lt;0.01,ABS(H32-J32)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>113509.18</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="33">
@@ -2329,27 +2545,34 @@
         <v>102610.73</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>15.33</v>
+        <v>15.3317013243775</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>15.33</v>
       </c>
-      <c r="G33" s="11" t="n">
-        <v>15.33</v>
+      <c r="G33" s="11">
+        <f>IFERROR((D33-L33)/L33*100,"")</f>
+        <v/>
       </c>
       <c r="H33" s="12" t="n">
-        <v>2.5644</v>
+        <v>2.564369816623821</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>2.5644</v>
       </c>
-      <c r="J33" s="12" t="n">
-        <v>2.5644</v>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J33" s="12">
+        <f>IFERROR(D33/M33*100,"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="7">
+        <f>IF(AND(ABS(E33-F33)&lt;0.01,ABS(E33-G33)&lt;0.01,ABS(H33-I33)&lt;0.01,ABS(H33-J33)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>88970.10000000001</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="34">
@@ -2372,27 +2595,34 @@
         <v>88897.28</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>5.45</v>
+        <v>5.452600037722109</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>5.45</v>
       </c>
-      <c r="G34" s="11" t="n">
-        <v>5.45</v>
+      <c r="G34" s="11">
+        <f>IFERROR((D34-L34)/L34*100,"")</f>
+        <v/>
       </c>
       <c r="H34" s="12" t="n">
-        <v>2.2217</v>
+        <v>2.221653638093759</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>2.2217</v>
       </c>
-      <c r="J34" s="12" t="n">
-        <v>2.2217</v>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J34" s="12">
+        <f>IFERROR(D34/M34*100,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="7">
+        <f>IF(AND(ABS(E34-F34)&lt;0.01,ABS(E34-G34)&lt;0.01,ABS(H34-I34)&lt;0.01,ABS(H34-J34)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>84300.7</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="35">
@@ -2415,27 +2645,34 @@
         <v>59182.67</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>-2.29</v>
+        <v>-2.292038200471587</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>-2.29</v>
       </c>
-      <c r="G35" s="11" t="n">
-        <v>-2.29</v>
+      <c r="G35" s="11">
+        <f>IFERROR((D35-L35)/L35*100,"")</f>
+        <v/>
       </c>
       <c r="H35" s="12" t="n">
-        <v>1.479</v>
+        <v>1.479048561638808</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>1.479</v>
       </c>
-      <c r="J35" s="12" t="n">
-        <v>1.479</v>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J35" s="12">
+        <f>IFERROR(D35/M35*100,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="7">
+        <f>IF(AND(ABS(E35-F35)&lt;0.01,ABS(E35-G35)&lt;0.01,ABS(H35-I35)&lt;0.01,ABS(H35-J35)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>60570.98</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="36">
@@ -2458,27 +2695,34 @@
         <v>57008.64</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>2.44</v>
+        <v>2.443739506723686</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>2.44</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>2.44</v>
+      <c r="G36" s="11">
+        <f>IFERROR((D36-L36)/L36*100,"")</f>
+        <v/>
       </c>
       <c r="H36" s="12" t="n">
-        <v>1.4247</v>
+        <v>1.4247168468909</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>1.4247</v>
       </c>
-      <c r="J36" s="12" t="n">
-        <v>1.4247</v>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J36" s="12">
+        <f>IFERROR(D36/M36*100,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="7">
+        <f>IF(AND(ABS(E36-F36)&lt;0.01,ABS(E36-G36)&lt;0.01,ABS(H36-I36)&lt;0.01,ABS(H36-J36)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>55648.73</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="37">
@@ -2501,27 +2745,34 @@
         <v>52730.58</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>10.82</v>
+        <v>10.81610445222393</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>10.82</v>
       </c>
-      <c r="G37" s="11" t="n">
-        <v>10.82</v>
+      <c r="G37" s="11">
+        <f>IFERROR((D37-L37)/L37*100,"")</f>
+        <v/>
       </c>
       <c r="H37" s="12" t="n">
-        <v>1.3178</v>
+        <v>1.317802804492939</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>1.3178</v>
       </c>
-      <c r="J37" s="12" t="n">
-        <v>1.3178</v>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J37" s="12">
+        <f>IFERROR(D37/M37*100,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="7">
+        <f>IF(AND(ABS(E37-F37)&lt;0.01,ABS(E37-G37)&lt;0.01,ABS(H37-I37)&lt;0.01,ABS(H37-J37)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>47583.86</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="38">
@@ -2544,27 +2795,34 @@
         <v>34637.79</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>13.49</v>
+        <v>13.49299601307482</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>13.49</v>
       </c>
-      <c r="G38" s="11" t="n">
-        <v>13.49</v>
+      <c r="G38" s="11">
+        <f>IFERROR((D38-L38)/L38*100,"")</f>
+        <v/>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0.8656</v>
+        <v>0.8656414703467603</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>0.8656</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>0.8656</v>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J38" s="12">
+        <f>IFERROR(D38/M38*100,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="7">
+        <f>IF(AND(ABS(E38-F38)&lt;0.01,ABS(E38-G38)&lt;0.01,ABS(H38-I38)&lt;0.01,ABS(H38-J38)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>30519.76</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="39">
@@ -2587,27 +2845,34 @@
         <v>28302.99</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>16.85</v>
+        <v>16.84726538164768</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>16.85</v>
       </c>
-      <c r="G39" s="11" t="n">
-        <v>16.85</v>
+      <c r="G39" s="11">
+        <f>IFERROR((D39-L39)/L39*100,"")</f>
+        <v/>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0.7073</v>
+        <v>0.7073269362395712</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0.7073</v>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>0.7073</v>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J39" s="12">
+        <f>IFERROR(D39/M39*100,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="7">
+        <f>IF(AND(ABS(E39-F39)&lt;0.01,ABS(E39-G39)&lt;0.01,ABS(H39-I39)&lt;0.01,ABS(H39-J39)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>24222.21</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="40">
@@ -2630,27 +2895,34 @@
         <v>13243.43</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>7.32</v>
+        <v>7.323933845934416</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>7.32</v>
       </c>
-      <c r="G40" s="11" t="n">
-        <v>7.32</v>
+      <c r="G40" s="11">
+        <f>IFERROR((D40-L40)/L40*100,"")</f>
+        <v/>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0.331</v>
+        <v>0.3309697939052808</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0.331</v>
       </c>
-      <c r="J40" s="12" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J40" s="12">
+        <f>IFERROR(D40/M40*100,"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="7">
+        <f>IF(AND(ABS(E40-F40)&lt;0.01,ABS(E40-G40)&lt;0.01,ABS(H40-I40)&lt;0.01,ABS(H40-J40)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>12339.68</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="41">
@@ -2673,27 +2945,34 @@
         <v>13206.85</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>4.64</v>
+        <v>4.640042721702031</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>4.64</v>
       </c>
-      <c r="G41" s="11" t="n">
-        <v>4.64</v>
+      <c r="G41" s="11">
+        <f>IFERROR((D41-L41)/L41*100,"")</f>
+        <v/>
       </c>
       <c r="H41" s="12" t="n">
-        <v>0.3301</v>
+        <v>0.3300556141904293</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0.3301</v>
       </c>
-      <c r="J41" s="12" t="n">
-        <v>0.3301</v>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J41" s="12">
+        <f>IFERROR(D41/M41*100,"")</f>
+        <v/>
+      </c>
+      <c r="K41" s="7">
+        <f>IF(AND(ABS(E41-F41)&lt;0.01,ABS(E41-G41)&lt;0.01,ABS(H41-I41)&lt;0.01,ABS(H41-J41)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>12621.22</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>4001401.41</v>
       </c>
     </row>
     <row r="42">
@@ -2716,27 +2995,34 @@
         <v>1352064.09</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>7.77</v>
+        <v>7.76824863966174</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>7.77</v>
       </c>
-      <c r="G42" s="11" t="n">
-        <v>7.77</v>
+      <c r="G42" s="11">
+        <f>IFERROR((D42-L42)/L42*100,"")</f>
+        <v/>
       </c>
       <c r="H42" s="12" t="n">
-        <v>35.9313</v>
+        <v>35.93130466423443</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>35.9313</v>
       </c>
-      <c r="J42" s="12" t="n">
-        <v>35.9313</v>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J42" s="12">
+        <f>IFERROR(D42/M42*100,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="7">
+        <f>IF(AND(ABS(E42-F42)&lt;0.01,ABS(E42-G42)&lt;0.01,ABS(H42-I42)&lt;0.01,ABS(H42-J42)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>1254603.38</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="43">
@@ -2759,27 +3045,34 @@
         <v>398181.91</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>11.71</v>
+        <v>11.71063431714138</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>11.71</v>
       </c>
-      <c r="G43" s="11" t="n">
-        <v>11.71</v>
+      <c r="G43" s="11">
+        <f>IFERROR((D43-L43)/L43*100,"")</f>
+        <v/>
       </c>
       <c r="H43" s="12" t="n">
-        <v>10.5817</v>
+        <v>10.58174359175294</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>10.5817</v>
       </c>
-      <c r="J43" s="12" t="n">
-        <v>10.5817</v>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J43" s="12">
+        <f>IFERROR(D43/M43*100,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="7">
+        <f>IF(AND(ABS(E43-F43)&lt;0.01,ABS(E43-G43)&lt;0.01,ABS(H43-I43)&lt;0.01,ABS(H43-J43)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>356440.47</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="44">
@@ -2802,27 +3095,34 @@
         <v>266609.87</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>10.69</v>
+        <v>10.68788562619892</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>10.69</v>
       </c>
-      <c r="G44" s="11" t="n">
-        <v>10.69</v>
+      <c r="G44" s="11">
+        <f>IFERROR((D44-L44)/L44*100,"")</f>
+        <v/>
       </c>
       <c r="H44" s="12" t="n">
-        <v>7.0852</v>
+        <v>7.085197023065626</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>7.0852</v>
       </c>
-      <c r="J44" s="12" t="n">
-        <v>7.0852</v>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J44" s="12">
+        <f>IFERROR(D44/M44*100,"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="7">
+        <f>IF(AND(ABS(E44-F44)&lt;0.01,ABS(E44-G44)&lt;0.01,ABS(H44-I44)&lt;0.01,ABS(H44-J44)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>240866.35</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="45">
@@ -2845,27 +3145,34 @@
         <v>255274.6</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>6.17</v>
+        <v>6.169679356044488</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>6.17</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <v>6.17</v>
+      <c r="G45" s="11">
+        <f>IFERROR((D45-L45)/L45*100,"")</f>
+        <v/>
       </c>
       <c r="H45" s="12" t="n">
-        <v>6.784</v>
+        <v>6.783960533735186</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>6.784</v>
       </c>
-      <c r="J45" s="12" t="n">
-        <v>6.784</v>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J45" s="12">
+        <f>IFERROR(D45/M45*100,"")</f>
+        <v/>
+      </c>
+      <c r="K45" s="7">
+        <f>IF(AND(ABS(E45-F45)&lt;0.01,ABS(E45-G45)&lt;0.01,ABS(H45-I45)&lt;0.01,ABS(H45-J45)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>240440.21</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="46">
@@ -2888,27 +3195,34 @@
         <v>254949.62</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>11.72</v>
+        <v>11.72018580591061</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>11.72</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>11.72</v>
+      <c r="G46" s="11">
+        <f>IFERROR((D46-L46)/L46*100,"")</f>
+        <v/>
       </c>
       <c r="H46" s="12" t="n">
-        <v>6.7753</v>
+        <v>6.775324141809576</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>6.7753</v>
       </c>
-      <c r="J46" s="12" t="n">
-        <v>6.7753</v>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J46" s="12">
+        <f>IFERROR(D46/M46*100,"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="7">
+        <f>IF(AND(ABS(E46-F46)&lt;0.01,ABS(E46-G46)&lt;0.01,ABS(H46-I46)&lt;0.01,ABS(H46-J46)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>228203.72</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="47">
@@ -2931,27 +3245,34 @@
         <v>206408.48</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>10.78</v>
+        <v>10.7820299607996</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>10.78</v>
       </c>
-      <c r="G47" s="11" t="n">
-        <v>10.78</v>
+      <c r="G47" s="11">
+        <f>IFERROR((D47-L47)/L47*100,"")</f>
+        <v/>
       </c>
       <c r="H47" s="12" t="n">
-        <v>5.4853</v>
+        <v>5.485336113143527</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>5.4853</v>
       </c>
-      <c r="J47" s="12" t="n">
-        <v>5.4853</v>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J47" s="12">
+        <f>IFERROR(D47/M47*100,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="7">
+        <f>IF(AND(ABS(E47-F47)&lt;0.01,ABS(E47-G47)&lt;0.01,ABS(H47-I47)&lt;0.01,ABS(H47-J47)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>186319.46</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="48">
@@ -2974,27 +3295,34 @@
         <v>203740.49</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>8.890000000000001</v>
+        <v>8.890386435413834</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="G48" s="11" t="n">
-        <v>8.890000000000001</v>
+      <c r="G48" s="11">
+        <f>IFERROR((D48-L48)/L48*100,"")</f>
+        <v/>
       </c>
       <c r="H48" s="12" t="n">
-        <v>5.4144</v>
+        <v>5.414433881333546</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>5.4144</v>
       </c>
-      <c r="J48" s="12" t="n">
-        <v>5.4144</v>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J48" s="12">
+        <f>IFERROR(D48/M48*100,"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="7">
+        <f>IF(AND(ABS(E48-F48)&lt;0.01,ABS(E48-G48)&lt;0.01,ABS(H48-I48)&lt;0.01,ABS(H48-J48)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>187106.04</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="49">
@@ -3017,27 +3345,34 @@
         <v>150054.36</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>17.21</v>
+        <v>17.20953033814727</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>17.21</v>
       </c>
-      <c r="G49" s="11" t="n">
-        <v>17.21</v>
+      <c r="G49" s="11">
+        <f>IFERROR((D49-L49)/L49*100,"")</f>
+        <v/>
       </c>
       <c r="H49" s="12" t="n">
-        <v>3.9877</v>
+        <v>3.987716976757154</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>3.9877</v>
       </c>
-      <c r="J49" s="12" t="n">
-        <v>3.9877</v>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J49" s="12">
+        <f>IFERROR(D49/M49*100,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="7">
+        <f>IF(AND(ABS(E49-F49)&lt;0.01,ABS(E49-G49)&lt;0.01,ABS(H49-I49)&lt;0.01,ABS(H49-J49)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>128022.32</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="50">
@@ -3060,27 +3395,34 @@
         <v>145344.16</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>10.46</v>
+        <v>10.46377573592085</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>10.46</v>
       </c>
-      <c r="G50" s="11" t="n">
-        <v>10.46</v>
+      <c r="G50" s="11">
+        <f>IFERROR((D50-L50)/L50*100,"")</f>
+        <v/>
       </c>
       <c r="H50" s="12" t="n">
-        <v>3.8625</v>
+        <v>3.862542709885325</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>3.8625</v>
       </c>
-      <c r="J50" s="12" t="n">
-        <v>3.8625</v>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J50" s="12">
+        <f>IFERROR(D50/M50*100,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="7">
+        <f>IF(AND(ABS(E50-F50)&lt;0.01,ABS(E50-G50)&lt;0.01,ABS(H50-I50)&lt;0.01,ABS(H50-J50)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>131576.31</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="51">
@@ -3103,27 +3445,34 @@
         <v>113509.18</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>6.31</v>
+        <v>6.31413689455951</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>6.31</v>
       </c>
-      <c r="G51" s="11" t="n">
-        <v>6.31</v>
+      <c r="G51" s="11">
+        <f>IFERROR((D51-L51)/L51*100,"")</f>
+        <v/>
       </c>
       <c r="H51" s="12" t="n">
-        <v>3.0165</v>
+        <v>3.016523372621652</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>3.0165</v>
       </c>
-      <c r="J51" s="12" t="n">
-        <v>3.0165</v>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J51" s="12">
+        <f>IFERROR(D51/M51*100,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="7">
+        <f>IF(AND(ABS(E51-F51)&lt;0.01,ABS(E51-G51)&lt;0.01,ABS(H51-I51)&lt;0.01,ABS(H51-J51)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>106767.72</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="52">
@@ -3146,27 +3495,34 @@
         <v>88970.10000000001</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>6.21</v>
+        <v>6.205284784310522</v>
       </c>
       <c r="F52" s="11" t="n">
         <v>6.21</v>
       </c>
-      <c r="G52" s="11" t="n">
-        <v>6.21</v>
+      <c r="G52" s="11">
+        <f>IFERROR((D52-L52)/L52*100,"")</f>
+        <v/>
       </c>
       <c r="H52" s="12" t="n">
-        <v>2.3644</v>
+        <v>2.364393665027672</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>2.3644</v>
       </c>
-      <c r="J52" s="12" t="n">
-        <v>2.3644</v>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J52" s="12">
+        <f>IFERROR(D52/M52*100,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="7">
+        <f>IF(AND(ABS(E52-F52)&lt;0.01,ABS(E52-G52)&lt;0.01,ABS(H52-I52)&lt;0.01,ABS(H52-J52)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>83771.82000000001</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="53">
@@ -3189,27 +3545,34 @@
         <v>84300.7</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3.54</v>
+        <v>3.536751679909767</v>
       </c>
       <c r="F53" s="11" t="n">
         <v>3.54</v>
       </c>
-      <c r="G53" s="11" t="n">
-        <v>3.54</v>
+      <c r="G53" s="11">
+        <f>IFERROR((D53-L53)/L53*100,"")</f>
+        <v/>
       </c>
       <c r="H53" s="12" t="n">
-        <v>2.2403</v>
+        <v>2.240303664235493</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>2.2403</v>
       </c>
-      <c r="J53" s="12" t="n">
-        <v>2.2403</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J53" s="12">
+        <f>IFERROR(D53/M53*100,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="7">
+        <f>IF(AND(ABS(E53-F53)&lt;0.01,ABS(E53-G53)&lt;0.01,ABS(H53-I53)&lt;0.01,ABS(H53-J53)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>81421.03999999999</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="54">
@@ -3232,27 +3595,34 @@
         <v>60570.98</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>6.08</v>
+        <v>6.078625459018624</v>
       </c>
       <c r="F54" s="11" t="n">
         <v>6.08</v>
       </c>
-      <c r="G54" s="11" t="n">
-        <v>6.08</v>
+      <c r="G54" s="11">
+        <f>IFERROR((D54-L54)/L54*100,"")</f>
+        <v/>
       </c>
       <c r="H54" s="12" t="n">
-        <v>1.6097</v>
+        <v>1.609682819245092</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>1.6097</v>
       </c>
-      <c r="J54" s="12" t="n">
-        <v>1.6097</v>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J54" s="12">
+        <f>IFERROR(D54/M54*100,"")</f>
+        <v/>
+      </c>
+      <c r="K54" s="7">
+        <f>IF(AND(ABS(E54-F54)&lt;0.01,ABS(E54-G54)&lt;0.01,ABS(H54-I54)&lt;0.01,ABS(H54-J54)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>57100.08</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="55">
@@ -3275,27 +3645,34 @@
         <v>55648.73</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>3.7</v>
+        <v>3.695056903145867</v>
       </c>
       <c r="F55" s="11" t="n">
         <v>3.7</v>
       </c>
-      <c r="G55" s="11" t="n">
-        <v>3.7</v>
+      <c r="G55" s="11">
+        <f>IFERROR((D55-L55)/L55*100,"")</f>
+        <v/>
       </c>
       <c r="H55" s="12" t="n">
-        <v>1.4789</v>
+        <v>1.478873292025471</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>1.4789</v>
       </c>
-      <c r="J55" s="12" t="n">
-        <v>1.4789</v>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J55" s="12">
+        <f>IFERROR(D55/M55*100,"")</f>
+        <v/>
+      </c>
+      <c r="K55" s="7">
+        <f>IF(AND(ABS(E55-F55)&lt;0.01,ABS(E55-G55)&lt;0.01,ABS(H55-I55)&lt;0.01,ABS(H55-J55)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>53665.75</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="56">
@@ -3318,27 +3695,34 @@
         <v>47583.86</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>6.26</v>
+        <v>6.257092722001921</v>
       </c>
       <c r="F56" s="11" t="n">
         <v>6.26</v>
       </c>
-      <c r="G56" s="11" t="n">
-        <v>6.26</v>
+      <c r="G56" s="11">
+        <f>IFERROR((D56-L56)/L56*100,"")</f>
+        <v/>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1.2645</v>
+        <v>1.264548170020755</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>1.2645</v>
       </c>
-      <c r="J56" s="12" t="n">
-        <v>1.2645</v>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J56" s="12">
+        <f>IFERROR(D56/M56*100,"")</f>
+        <v/>
+      </c>
+      <c r="K56" s="7">
+        <f>IF(AND(ABS(E56-F56)&lt;0.01,ABS(E56-G56)&lt;0.01,ABS(H56-I56)&lt;0.01,ABS(H56-J56)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>44781.82</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="57">
@@ -3361,27 +3745,34 @@
         <v>30519.76</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>32.87</v>
+        <v>32.8709226329895</v>
       </c>
       <c r="F57" s="11" t="n">
         <v>32.87</v>
       </c>
-      <c r="G57" s="11" t="n">
-        <v>32.87</v>
+      <c r="G57" s="11">
+        <f>IFERROR((D57-L57)/L57*100,"")</f>
+        <v/>
       </c>
       <c r="H57" s="12" t="n">
-        <v>0.8111</v>
+        <v>0.8110671697813641</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0.8111</v>
       </c>
-      <c r="J57" s="12" t="n">
-        <v>0.8111</v>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J57" s="12">
+        <f>IFERROR(D57/M57*100,"")</f>
+        <v/>
+      </c>
+      <c r="K57" s="7">
+        <f>IF(AND(ABS(E57-F57)&lt;0.01,ABS(E57-G57)&lt;0.01,ABS(H57-I57)&lt;0.01,ABS(H57-J57)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>22969.48</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="58">
@@ -3404,27 +3795,34 @@
         <v>24222.21</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>10.57</v>
+        <v>10.57088078880697</v>
       </c>
       <c r="F58" s="11" t="n">
         <v>10.57</v>
       </c>
-      <c r="G58" s="11" t="n">
-        <v>10.57</v>
+      <c r="G58" s="11">
+        <f>IFERROR((D58-L58)/L58*100,"")</f>
+        <v/>
       </c>
       <c r="H58" s="12" t="n">
-        <v>0.6437</v>
+        <v>0.6437088401268507</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>0.6437</v>
       </c>
-      <c r="J58" s="12" t="n">
-        <v>0.6437</v>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J58" s="12">
+        <f>IFERROR(D58/M58*100,"")</f>
+        <v/>
+      </c>
+      <c r="K58" s="7">
+        <f>IF(AND(ABS(E58-F58)&lt;0.01,ABS(E58-G58)&lt;0.01,ABS(H58-I58)&lt;0.01,ABS(H58-J58)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>21906.5</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="59">
@@ -3447,27 +3845,34 @@
         <v>12621.22</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>4.41</v>
+        <v>4.412706344071964</v>
       </c>
       <c r="F59" s="11" t="n">
         <v>4.41</v>
       </c>
-      <c r="G59" s="11" t="n">
-        <v>4.41</v>
+      <c r="G59" s="11">
+        <f>IFERROR((D59-L59)/L59*100,"")</f>
+        <v/>
       </c>
       <c r="H59" s="12" t="n">
-        <v>0.3354</v>
+        <v>0.3354108022011951</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>0.3354</v>
       </c>
-      <c r="J59" s="12" t="n">
-        <v>0.3354</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J59" s="12">
+        <f>IFERROR(D59/M59*100,"")</f>
+        <v/>
+      </c>
+      <c r="K59" s="7">
+        <f>IF(AND(ABS(E59-F59)&lt;0.01,ABS(E59-G59)&lt;0.01,ABS(H59-I59)&lt;0.01,ABS(H59-J59)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>12087.82</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="60">
@@ -3490,27 +3895,34 @@
         <v>12339.68</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>26.22</v>
+        <v>26.22267320777568</v>
       </c>
       <c r="F60" s="11" t="n">
         <v>26.22</v>
       </c>
-      <c r="G60" s="11" t="n">
-        <v>26.22</v>
+      <c r="G60" s="11">
+        <f>IFERROR((D60-L60)/L60*100,"")</f>
+        <v/>
       </c>
       <c r="H60" s="12" t="n">
-        <v>0.3279</v>
+        <v>0.3279288347486252</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>0.3279</v>
       </c>
-      <c r="J60" s="12" t="n">
-        <v>0.3279</v>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J60" s="12">
+        <f>IFERROR(D60/M60*100,"")</f>
+        <v/>
+      </c>
+      <c r="K60" s="7">
+        <f>IF(AND(ABS(E60-F60)&lt;0.01,ABS(E60-G60)&lt;0.01,ABS(H60-I60)&lt;0.01,ABS(H60-J60)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>9776.120000000001</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>3762913.99</v>
       </c>
     </row>
     <row r="61">
@@ -3533,27 +3945,34 @@
         <v>1254603.38</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>1.83</v>
+        <v>1.829149668910454</v>
       </c>
       <c r="F61" s="11" t="n">
         <v>1.83</v>
       </c>
-      <c r="G61" s="11" t="n">
-        <v>1.83</v>
+      <c r="G61" s="11">
+        <f>IFERROR((D61-L61)/L61*100,"")</f>
+        <v/>
       </c>
       <c r="H61" s="12" t="n">
-        <v>36.3882</v>
+        <v>36.38824079780674</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>36.3882</v>
       </c>
-      <c r="J61" s="12" t="n">
-        <v>36.3882</v>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J61" s="12">
+        <f>IFERROR(D61/M61*100,"")</f>
+        <v/>
+      </c>
+      <c r="K61" s="7">
+        <f>IF(AND(ABS(E61-F61)&lt;0.01,ABS(E61-G61)&lt;0.01,ABS(H61-I61)&lt;0.01,ABS(H61-J61)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>1232067.03</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="62">
@@ -3576,27 +3995,34 @@
         <v>356440.47</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>22.57</v>
+        <v>22.57150370353277</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>22.57</v>
       </c>
-      <c r="G62" s="11" t="n">
-        <v>22.57</v>
+      <c r="G62" s="11">
+        <f>IFERROR((D62-L62)/L62*100,"")</f>
+        <v/>
       </c>
       <c r="H62" s="12" t="n">
-        <v>10.3381</v>
+        <v>10.33812108209322</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>10.3381</v>
       </c>
-      <c r="J62" s="12" t="n">
-        <v>10.3381</v>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J62" s="12">
+        <f>IFERROR(D62/M62*100,"")</f>
+        <v/>
+      </c>
+      <c r="K62" s="7">
+        <f>IF(AND(ABS(E62-F62)&lt;0.01,ABS(E62-G62)&lt;0.01,ABS(H62-I62)&lt;0.01,ABS(H62-J62)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>290802.07</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="63">
@@ -3619,27 +4045,34 @@
         <v>240866.35</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.31</v>
+        <v>1.308138501726366</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>1.31</v>
       </c>
-      <c r="G63" s="11" t="n">
-        <v>1.31</v>
+      <c r="G63" s="11">
+        <f>IFERROR((D63-L63)/L63*100,"")</f>
+        <v/>
       </c>
       <c r="H63" s="12" t="n">
-        <v>6.986</v>
+        <v>6.986034697187569</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>6.986</v>
       </c>
-      <c r="J63" s="12" t="n">
-        <v>6.986</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J63" s="12">
+        <f>IFERROR(D63/M63*100,"")</f>
+        <v/>
+      </c>
+      <c r="K63" s="7">
+        <f>IF(AND(ABS(E63-F63)&lt;0.01,ABS(E63-G63)&lt;0.01,ABS(H63-I63)&lt;0.01,ABS(H63-J63)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>237756.17</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="64">
@@ -3662,27 +4095,34 @@
         <v>240440.21</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>9.369999999999999</v>
+        <v>9.37333781124963</v>
       </c>
       <c r="F64" s="11" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="G64" s="11" t="n">
-        <v>9.369999999999999</v>
+      <c r="G64" s="11">
+        <f>IFERROR((D64-L64)/L64*100,"")</f>
+        <v/>
       </c>
       <c r="H64" s="12" t="n">
-        <v>6.9737</v>
+        <v>6.973675026250306</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>6.9737</v>
       </c>
-      <c r="J64" s="12" t="n">
-        <v>6.9737</v>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J64" s="12">
+        <f>IFERROR(D64/M64*100,"")</f>
+        <v/>
+      </c>
+      <c r="K64" s="7">
+        <f>IF(AND(ABS(E64-F64)&lt;0.01,ABS(E64-G64)&lt;0.01,ABS(H64-I64)&lt;0.01,ABS(H64-J64)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>219834.39</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="65">
@@ -3705,27 +4145,34 @@
         <v>228203.72</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>6.65</v>
+        <v>6.654785585779941</v>
       </c>
       <c r="F65" s="11" t="n">
         <v>6.65</v>
       </c>
-      <c r="G65" s="11" t="n">
-        <v>6.65</v>
+      <c r="G65" s="11">
+        <f>IFERROR((D65-L65)/L65*100,"")</f>
+        <v/>
       </c>
       <c r="H65" s="12" t="n">
-        <v>6.6188</v>
+        <v>6.618770558640827</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>6.6188</v>
       </c>
-      <c r="J65" s="12" t="n">
-        <v>6.6188</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J65" s="12">
+        <f>IFERROR(D65/M65*100,"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="7">
+        <f>IF(AND(ABS(E65-F65)&lt;0.01,ABS(E65-G65)&lt;0.01,ABS(H65-I65)&lt;0.01,ABS(H65-J65)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>213964.82</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="66">
@@ -3748,27 +4195,34 @@
         <v>187106.04</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>10.31</v>
+        <v>10.30912500568182</v>
       </c>
       <c r="F66" s="11" t="n">
         <v>10.31</v>
       </c>
-      <c r="G66" s="11" t="n">
-        <v>10.31</v>
+      <c r="G66" s="11">
+        <f>IFERROR((D66-L66)/L66*100,"")</f>
+        <v/>
       </c>
       <c r="H66" s="12" t="n">
-        <v>5.4268</v>
+        <v>5.426782477059852</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>5.4268</v>
       </c>
-      <c r="J66" s="12" t="n">
-        <v>5.4268</v>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J66" s="12">
+        <f>IFERROR(D66/M66*100,"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="7">
+        <f>IF(AND(ABS(E66-F66)&lt;0.01,ABS(E66-G66)&lt;0.01,ABS(H66-I66)&lt;0.01,ABS(H66-J66)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>169619.73</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="67">
@@ -3791,27 +4245,34 @@
         <v>186319.46</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>6.8</v>
+        <v>6.804985408855847</v>
       </c>
       <c r="F67" s="11" t="n">
         <v>6.8</v>
       </c>
-      <c r="G67" s="11" t="n">
-        <v>6.8</v>
+      <c r="G67" s="11">
+        <f>IFERROR((D67-L67)/L67*100,"")</f>
+        <v/>
       </c>
       <c r="H67" s="12" t="n">
-        <v>5.404</v>
+        <v>5.403968683551071</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>5.404</v>
       </c>
-      <c r="J67" s="12" t="n">
-        <v>5.404</v>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J67" s="12">
+        <f>IFERROR(D67/M67*100,"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="7">
+        <f>IF(AND(ABS(E67-F67)&lt;0.01,ABS(E67-G67)&lt;0.01,ABS(H67-I67)&lt;0.01,ABS(H67-J67)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>174448.28</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="68">
@@ -3834,27 +4295,34 @@
         <v>131576.31</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>8.65</v>
+        <v>8.645126397014197</v>
       </c>
       <c r="F68" s="11" t="n">
         <v>8.65</v>
       </c>
-      <c r="G68" s="11" t="n">
-        <v>8.65</v>
+      <c r="G68" s="11">
+        <f>IFERROR((D68-L68)/L68*100,"")</f>
+        <v/>
       </c>
       <c r="H68" s="12" t="n">
-        <v>3.8162</v>
+        <v>3.816210387992792</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>3.8162</v>
       </c>
-      <c r="J68" s="12" t="n">
-        <v>3.8162</v>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J68" s="12">
+        <f>IFERROR(D68/M68*100,"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="7">
+        <f>IF(AND(ABS(E68-F68)&lt;0.01,ABS(E68-G68)&lt;0.01,ABS(H68-I68)&lt;0.01,ABS(H68-J68)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>121106.5</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="69">
@@ -3877,27 +4345,34 @@
         <v>128022.32</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>23.51</v>
+        <v>23.50663341701701</v>
       </c>
       <c r="F69" s="11" t="n">
         <v>23.51</v>
       </c>
-      <c r="G69" s="11" t="n">
-        <v>23.51</v>
+      <c r="G69" s="11">
+        <f>IFERROR((D69-L69)/L69*100,"")</f>
+        <v/>
       </c>
       <c r="H69" s="12" t="n">
-        <v>3.7131</v>
+        <v>3.713131242842556</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>3.7131</v>
       </c>
-      <c r="J69" s="12" t="n">
-        <v>3.7131</v>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J69" s="12">
+        <f>IFERROR(D69/M69*100,"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="7">
+        <f>IF(AND(ABS(E69-F69)&lt;0.01,ABS(E69-G69)&lt;0.01,ABS(H69-I69)&lt;0.01,ABS(H69-J69)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>103656.23</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="70">
@@ -3920,27 +4395,34 @@
         <v>106767.72</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.359972268510727</v>
       </c>
       <c r="F70" s="11" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="G70" s="11" t="n">
-        <v>8.359999999999999</v>
+      <c r="G70" s="11">
+        <f>IFERROR((D70-L70)/L70*100,"")</f>
+        <v/>
       </c>
       <c r="H70" s="12" t="n">
-        <v>3.0967</v>
+        <v>3.096667494067175</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>3.0967</v>
       </c>
-      <c r="J70" s="12" t="n">
-        <v>3.0967</v>
-      </c>
-      <c r="K70" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J70" s="12">
+        <f>IFERROR(D70/M70*100,"")</f>
+        <v/>
+      </c>
+      <c r="K70" s="7">
+        <f>IF(AND(ABS(E70-F70)&lt;0.01,ABS(E70-G70)&lt;0.01,ABS(H70-I70)&lt;0.01,ABS(H70-J70)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>98530.59</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="71">
@@ -3963,27 +4445,34 @@
         <v>83771.82000000001</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>8.57</v>
+        <v>8.565230903133722</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>8.57</v>
       </c>
-      <c r="G71" s="11" t="n">
-        <v>8.57</v>
+      <c r="G71" s="11">
+        <f>IFERROR((D71-L71)/L71*100,"")</f>
+        <v/>
       </c>
       <c r="H71" s="12" t="n">
-        <v>2.4297</v>
+        <v>2.429699462654504</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>2.4297</v>
       </c>
-      <c r="J71" s="12" t="n">
-        <v>2.4297</v>
-      </c>
-      <c r="K71" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J71" s="12">
+        <f>IFERROR(D71/M71*100,"")</f>
+        <v/>
+      </c>
+      <c r="K71" s="7">
+        <f>IF(AND(ABS(E71-F71)&lt;0.01,ABS(E71-G71)&lt;0.01,ABS(H71-I71)&lt;0.01,ABS(H71-J71)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>77162.66</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="72">
@@ -4006,27 +4495,34 @@
         <v>81421.03999999999</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>9.48</v>
+        <v>9.477273537077847</v>
       </c>
       <c r="F72" s="11" t="n">
         <v>9.48</v>
       </c>
-      <c r="G72" s="11" t="n">
-        <v>9.48</v>
+      <c r="G72" s="11">
+        <f>IFERROR((D72-L72)/L72*100,"")</f>
+        <v/>
       </c>
       <c r="H72" s="12" t="n">
-        <v>2.3615</v>
+        <v>2.361517955999652</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>2.3615</v>
       </c>
-      <c r="J72" s="12" t="n">
-        <v>2.3615</v>
-      </c>
-      <c r="K72" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J72" s="12">
+        <f>IFERROR(D72/M72*100,"")</f>
+        <v/>
+      </c>
+      <c r="K72" s="7">
+        <f>IF(AND(ABS(E72-F72)&lt;0.01,ABS(E72-G72)&lt;0.01,ABS(H72-I72)&lt;0.01,ABS(H72-J72)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L72" s="13" t="n">
+        <v>74372.55</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="73">
@@ -4049,27 +4545,34 @@
         <v>57100.08</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>14.96</v>
+        <v>14.95715285152731</v>
       </c>
       <c r="F73" s="11" t="n">
         <v>14.96</v>
       </c>
-      <c r="G73" s="11" t="n">
-        <v>14.96</v>
+      <c r="G73" s="11">
+        <f>IFERROR((D73-L73)/L73*100,"")</f>
+        <v/>
       </c>
       <c r="H73" s="12" t="n">
-        <v>1.6561</v>
+        <v>1.656118175461977</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>1.6561</v>
       </c>
-      <c r="J73" s="12" t="n">
-        <v>1.6561</v>
-      </c>
-      <c r="K73" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J73" s="12">
+        <f>IFERROR(D73/M73*100,"")</f>
+        <v/>
+      </c>
+      <c r="K73" s="7">
+        <f>IF(AND(ABS(E73-F73)&lt;0.01,ABS(E73-G73)&lt;0.01,ABS(H73-I73)&lt;0.01,ABS(H73-J73)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L73" s="13" t="n">
+        <v>49670.75</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="74">
@@ -4092,27 +4595,34 @@
         <v>53665.75</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.110413910139771</v>
       </c>
       <c r="F74" s="11" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="G74" s="11" t="n">
-        <v>8.109999999999999</v>
+      <c r="G74" s="11">
+        <f>IFERROR((D74-L74)/L74*100,"")</f>
+        <v/>
       </c>
       <c r="H74" s="12" t="n">
-        <v>1.5565</v>
+        <v>1.556509622662501</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>1.5565</v>
       </c>
-      <c r="J74" s="12" t="n">
-        <v>1.5565</v>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J74" s="12">
+        <f>IFERROR(D74/M74*100,"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="7">
+        <f>IF(AND(ABS(E74-F74)&lt;0.01,ABS(E74-G74)&lt;0.01,ABS(H74-I74)&lt;0.01,ABS(H74-J74)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L74" s="13" t="n">
+        <v>49639.76</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="75">
@@ -4135,27 +4645,34 @@
         <v>44781.82</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>6.28</v>
+        <v>6.276010221827325</v>
       </c>
       <c r="F75" s="11" t="n">
         <v>6.28</v>
       </c>
-      <c r="G75" s="11" t="n">
-        <v>6.28</v>
+      <c r="G75" s="11">
+        <f>IFERROR((D75-L75)/L75*100,"")</f>
+        <v/>
       </c>
       <c r="H75" s="12" t="n">
-        <v>1.2988</v>
+        <v>1.298842068737323</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>1.2988</v>
       </c>
-      <c r="J75" s="12" t="n">
-        <v>1.2988</v>
-      </c>
-      <c r="K75" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J75" s="12">
+        <f>IFERROR(D75/M75*100,"")</f>
+        <v/>
+      </c>
+      <c r="K75" s="7">
+        <f>IF(AND(ABS(E75-F75)&lt;0.01,ABS(E75-G75)&lt;0.01,ABS(H75-I75)&lt;0.01,ABS(H75-J75)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L75" s="13" t="n">
+        <v>42137.28</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="76">
@@ -4178,27 +4695,34 @@
         <v>22969.48</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>29.9</v>
+        <v>29.8978890125501</v>
       </c>
       <c r="F76" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="G76" s="11" t="n">
-        <v>29.9</v>
+      <c r="G76" s="11">
+        <f>IFERROR((D76-L76)/L76*100,"")</f>
+        <v/>
       </c>
       <c r="H76" s="12" t="n">
-        <v>0.6662</v>
+        <v>0.6662017515371322</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0.6662</v>
       </c>
-      <c r="J76" s="12" t="n">
-        <v>0.6662</v>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J76" s="12">
+        <f>IFERROR(D76/M76*100,"")</f>
+        <v/>
+      </c>
+      <c r="K76" s="7">
+        <f>IF(AND(ABS(E76-F76)&lt;0.01,ABS(E76-G76)&lt;0.01,ABS(H76-I76)&lt;0.01,ABS(H76-J76)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L76" s="13" t="n">
+        <v>17682.72</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="77">
@@ -4221,27 +4745,34 @@
         <v>21906.5</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>23.67</v>
+        <v>23.67365488351873</v>
       </c>
       <c r="F77" s="11" t="n">
         <v>23.67</v>
       </c>
-      <c r="G77" s="11" t="n">
-        <v>23.67</v>
+      <c r="G77" s="11">
+        <f>IFERROR((D77-L77)/L77*100,"")</f>
+        <v/>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0.6354</v>
+        <v>0.6353713131532881</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>0.6354</v>
       </c>
-      <c r="J77" s="12" t="n">
-        <v>0.6354</v>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J77" s="12">
+        <f>IFERROR(D77/M77*100,"")</f>
+        <v/>
+      </c>
+      <c r="K77" s="7">
+        <f>IF(AND(ABS(E77-F77)&lt;0.01,ABS(E77-G77)&lt;0.01,ABS(H77-I77)&lt;0.01,ABS(H77-J77)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L77" s="13" t="n">
+        <v>17713.15</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="78">
@@ -4264,27 +4795,34 @@
         <v>12087.82</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>3.23</v>
+        <v>3.233084954202872</v>
       </c>
       <c r="F78" s="11" t="n">
         <v>3.23</v>
       </c>
-      <c r="G78" s="11" t="n">
-        <v>3.23</v>
+      <c r="G78" s="11">
+        <f>IFERROR((D78-L78)/L78*100,"")</f>
+        <v/>
       </c>
       <c r="H78" s="12" t="n">
-        <v>0.3506</v>
+        <v>0.3505924755922022</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>0.3506</v>
       </c>
-      <c r="J78" s="12" t="n">
-        <v>0.3506</v>
-      </c>
-      <c r="K78" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J78" s="12">
+        <f>IFERROR(D78/M78*100,"")</f>
+        <v/>
+      </c>
+      <c r="K78" s="7">
+        <f>IF(AND(ABS(E78-F78)&lt;0.01,ABS(E78-G78)&lt;0.01,ABS(H78-I78)&lt;0.01,ABS(H78-J78)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L78" s="13" t="n">
+        <v>11709.25</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
     <row r="79">
@@ -4307,27 +4845,34 @@
         <v>9776.120000000001</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>35.3</v>
+        <v>35.29782178163012</v>
       </c>
       <c r="F79" s="11" t="n">
         <v>35.3</v>
       </c>
-      <c r="G79" s="11" t="n">
-        <v>35.3</v>
+      <c r="G79" s="11">
+        <f>IFERROR((D79-L79)/L79*100,"")</f>
+        <v/>
       </c>
       <c r="H79" s="12" t="n">
-        <v>0.2835</v>
+        <v>0.2835444366714958</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>0.2835</v>
       </c>
-      <c r="J79" s="12" t="n">
-        <v>0.2835</v>
-      </c>
-      <c r="K79" s="7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
+      <c r="J79" s="12">
+        <f>IFERROR(D79/M79*100,"")</f>
+        <v/>
+      </c>
+      <c r="K79" s="7">
+        <f>IF(AND(ABS(E79-F79)&lt;0.01,ABS(E79-G79)&lt;0.01,ABS(H79-I79)&lt;0.01,ABS(H79-J79)&lt;0.01),"MATCH","MISMATCH")</f>
+        <v/>
+      </c>
+      <c r="L79" s="13" t="n">
+        <v>7225.63</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>3447826.42</v>
       </c>
     </row>
   </sheetData>
@@ -4348,7 +4893,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -4372,7 +4917,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Total Mutually Exclusive Credit (₹ Cr)</t>
+          <t>Total Mutually Exclusive Credit (â‚¹ Cr)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -4410,13 +4955,13 @@
       <c r="B4" s="10" t="n">
         <v>2715406.47</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="14" t="n">
         <v>1713.94</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>0.1714</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>56.84</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -4437,13 +4982,13 @@
       <c r="B5" s="10" t="n">
         <v>2745352.94</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>1698.84</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>0.1699</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>56.54</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -4464,13 +5009,13 @@
       <c r="B6" s="10" t="n">
         <v>2837528.33</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>1757.88</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>0.1758</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>56.98</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -4491,13 +5036,13 @@
       <c r="B7" s="10" t="n">
         <v>2817879.12</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>1792.49</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>0.1792</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>57.06</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -4518,13 +5063,13 @@
       <c r="B8" s="10" t="n">
         <v>2771471.96</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>1805.44</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>0.1805</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>57.06</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -4545,13 +5090,13 @@
       <c r="B9" s="10" t="n">
         <v>2780229.12</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>1777.92</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.1778</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>56.56</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -4572,13 +5117,13 @@
       <c r="B10" s="10" t="n">
         <v>2761535.02</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>1793.28</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>0.1793</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>56.82</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -4599,13 +5144,13 @@
       <c r="B11" s="10" t="n">
         <v>2737075.98</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>1745.16</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>0.1745</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>56.16</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -4626,13 +5171,13 @@
       <c r="B12" s="10" t="n">
         <v>2730943.18</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>1752.17</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>0.1752</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>56.15</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4653,13 +5198,13 @@
       <c r="B13" s="10" t="n">
         <v>2892418.98</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>1745.66</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>0.1746</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>56.08</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4680,13 +5225,13 @@
       <c r="B14" s="10" t="n">
         <v>2866553.89</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>1780.88</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>0.1781</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>56.49</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -4707,13 +5252,13 @@
       <c r="B15" s="10" t="n">
         <v>2848416.11</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>1771.79</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>0.1772</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>56.37</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4734,13 +5279,13 @@
       <c r="B16" s="10" t="n">
         <v>2869245.82</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>1759.84</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>0.176</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <v>56.08</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4761,13 +5306,13 @@
       <c r="B17" s="10" t="n">
         <v>2871313.05</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>1740.17</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>0.174</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <v>55.94</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -4788,13 +5333,13 @@
       <c r="B18" s="10" t="n">
         <v>2946851.25</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>1734.81</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>0.1735</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <v>55.73</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -4815,13 +5360,13 @@
       <c r="B19" s="10" t="n">
         <v>2928353.27</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>1749.76</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>0.175</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <v>55.76</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -4842,13 +5387,13 @@
       <c r="B20" s="10" t="n">
         <v>2904685.07</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>1787.09</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>0.1787</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <v>56.36</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -4869,13 +5414,13 @@
       <c r="B21" s="10" t="n">
         <v>2911362.69</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>1802.74</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>0.1803</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="15" t="n">
         <v>56.47</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -4896,13 +5441,13 @@
       <c r="B22" s="10" t="n">
         <v>2868970.47</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <v>1812.34</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>0.1812</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="15" t="n">
         <v>56.53</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -4923,13 +5468,13 @@
       <c r="B23" s="10" t="n">
         <v>2825014.64</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <v>1780.24</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>0.178</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="15" t="n">
         <v>56.33</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -4950,13 +5495,13 @@
       <c r="B24" s="10" t="n">
         <v>2831679.89</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="14" t="n">
         <v>1772.07</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>0.1772</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="15" t="n">
         <v>56.04</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -4977,13 +5522,13 @@
       <c r="B25" s="10" t="n">
         <v>2803794.83</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>1759.79</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>0.176</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="15" t="n">
         <v>55.87</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -5004,13 +5549,13 @@
       <c r="B26" s="10" t="n">
         <v>2817624.48</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>1766.99</v>
       </c>
       <c r="D26" s="12" t="n">
         <v>0.1767</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="15" t="n">
         <v>55.93</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -5031,13 +5576,13 @@
       <c r="B27" s="10" t="n">
         <v>2822924.36</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="14" t="n">
         <v>1738.34</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>0.1738</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="15" t="n">
         <v>55.26</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -5058,13 +5603,13 @@
       <c r="B28" s="10" t="n">
         <v>2945303.78</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="14" t="n">
         <v>1688.54</v>
       </c>
       <c r="D28" s="12" t="n">
         <v>0.1689</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>54.55</v>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -5085,13 +5630,13 @@
       <c r="B29" s="10" t="n">
         <v>2975110.72</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="14" t="n">
         <v>1682.66</v>
       </c>
       <c r="D29" s="12" t="n">
         <v>0.1683</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="15" t="n">
         <v>54.36</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -5112,13 +5657,13 @@
       <c r="B30" s="10" t="n">
         <v>2940570.71</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="14" t="n">
         <v>1787.24</v>
       </c>
       <c r="D30" s="12" t="n">
         <v>0.1787</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="15" t="n">
         <v>55.64</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -5139,13 +5684,13 @@
       <c r="B31" s="10" t="n">
         <v>2962892.47</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="14" t="n">
         <v>1754.52</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>0.1755</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="15" t="n">
         <v>54.92</v>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -5166,13 +5711,13 @@
       <c r="B32" s="10" t="n">
         <v>2957537.03</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C32" s="14" t="n">
         <v>1764.16</v>
       </c>
       <c r="D32" s="12" t="n">
         <v>0.1764</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="15" t="n">
         <v>54.99</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -5193,13 +5738,13 @@
       <c r="B33" s="10" t="n">
         <v>2941899.97</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="14" t="n">
         <v>1800.96</v>
       </c>
       <c r="D33" s="12" t="n">
         <v>0.1801</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="15" t="n">
         <v>55.38</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -5220,13 +5765,13 @@
       <c r="B34" s="10" t="n">
         <v>2934180.3</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="14" t="n">
         <v>1781.38</v>
       </c>
       <c r="D34" s="12" t="n">
         <v>0.1781</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="15" t="n">
         <v>54.89</v>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -5247,13 +5792,13 @@
       <c r="B35" s="10" t="n">
         <v>2922212.8</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <v>1791.66</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>0.1792</v>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E35" s="15" t="n">
         <v>55.03</v>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -5274,13 +5819,13 @@
       <c r="B36" s="10" t="n">
         <v>2939098.81</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="C36" s="14" t="n">
         <v>1785.82</v>
       </c>
       <c r="D36" s="12" t="n">
         <v>0.1786</v>
       </c>
-      <c r="E36" s="14" t="n">
+      <c r="E36" s="15" t="n">
         <v>54.79</v>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -5301,13 +5846,13 @@
       <c r="B37" s="10" t="n">
         <v>2954305.91</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="14" t="n">
         <v>1819.51</v>
       </c>
       <c r="D37" s="12" t="n">
         <v>0.182</v>
       </c>
-      <c r="E37" s="14" t="n">
+      <c r="E37" s="15" t="n">
         <v>55.06</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -5328,13 +5873,13 @@
       <c r="B38" s="10" t="n">
         <v>2977969.88</v>
       </c>
-      <c r="C38" s="13" t="n">
+      <c r="C38" s="14" t="n">
         <v>1807.44</v>
       </c>
       <c r="D38" s="12" t="n">
         <v>0.1807</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="E38" s="15" t="n">
         <v>54.95</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -5355,13 +5900,13 @@
       <c r="B39" s="10" t="n">
         <v>3087299.7</v>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="14" t="n">
         <v>1761.5</v>
       </c>
       <c r="D39" s="12" t="n">
         <v>0.1762</v>
       </c>
-      <c r="E39" s="14" t="n">
+      <c r="E39" s="15" t="n">
         <v>54.39</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -5382,13 +5927,13 @@
       <c r="B40" s="10" t="n">
         <v>3049445.91</v>
       </c>
-      <c r="C40" s="13" t="n">
+      <c r="C40" s="14" t="n">
         <v>1820.45</v>
       </c>
       <c r="D40" s="12" t="n">
         <v>0.182</v>
       </c>
-      <c r="E40" s="14" t="n">
+      <c r="E40" s="15" t="n">
         <v>54.9</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -5409,13 +5954,13 @@
       <c r="B41" s="10" t="n">
         <v>3102630.16</v>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="14" t="n">
         <v>1807.98</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>0.1808</v>
       </c>
-      <c r="E41" s="14" t="n">
+      <c r="E41" s="15" t="n">
         <v>54.84</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -5436,13 +5981,13 @@
       <c r="B42" s="10" t="n">
         <v>3181100.12</v>
       </c>
-      <c r="C42" s="13" t="n">
+      <c r="C42" s="14" t="n">
         <v>1791.87</v>
       </c>
       <c r="D42" s="12" t="n">
         <v>0.1792</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E42" s="15" t="n">
         <v>54.55</v>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -5463,13 +6008,13 @@
       <c r="B43" s="10" t="n">
         <v>3174821.16</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="14" t="n">
         <v>1812.08</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>0.1812</v>
       </c>
-      <c r="E43" s="14" t="n">
+      <c r="E43" s="15" t="n">
         <v>54.64</v>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -5490,13 +6035,13 @@
       <c r="B44" s="10" t="n">
         <v>3192957.81</v>
       </c>
-      <c r="C44" s="13" t="n">
+      <c r="C44" s="14" t="n">
         <v>1805.8</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>0.1806</v>
       </c>
-      <c r="E44" s="14" t="n">
+      <c r="E44" s="15" t="n">
         <v>54.78</v>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -5517,13 +6062,13 @@
       <c r="B45" s="10" t="n">
         <v>3209099.56</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="14" t="n">
         <v>1812.45</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>0.1812</v>
       </c>
-      <c r="E45" s="14" t="n">
+      <c r="E45" s="15" t="n">
         <v>54.86</v>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -5544,13 +6089,13 @@
       <c r="B46" s="10" t="n">
         <v>3214589.85</v>
       </c>
-      <c r="C46" s="13" t="n">
+      <c r="C46" s="14" t="n">
         <v>1813.84</v>
       </c>
       <c r="D46" s="12" t="n">
         <v>0.1814</v>
       </c>
-      <c r="E46" s="14" t="n">
+      <c r="E46" s="15" t="n">
         <v>54.82</v>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -5571,13 +6116,13 @@
       <c r="B47" s="10" t="n">
         <v>3232613.77</v>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="14" t="n">
         <v>1796.7</v>
       </c>
       <c r="D47" s="12" t="n">
         <v>0.1797</v>
       </c>
-      <c r="E47" s="14" t="n">
+      <c r="E47" s="15" t="n">
         <v>54.5</v>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -5598,13 +6143,13 @@
       <c r="B48" s="10" t="n">
         <v>3276479.33</v>
       </c>
-      <c r="C48" s="13" t="n">
+      <c r="C48" s="14" t="n">
         <v>1763.79</v>
       </c>
       <c r="D48" s="12" t="n">
         <v>0.1764</v>
       </c>
-      <c r="E48" s="14" t="n">
+      <c r="E48" s="15" t="n">
         <v>53.97</v>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -5625,13 +6170,13 @@
       <c r="B49" s="10" t="n">
         <v>3320589.43</v>
       </c>
-      <c r="C49" s="13" t="n">
+      <c r="C49" s="14" t="n">
         <v>1784.27</v>
       </c>
       <c r="D49" s="12" t="n">
         <v>0.1784</v>
       </c>
-      <c r="E49" s="14" t="n">
+      <c r="E49" s="15" t="n">
         <v>54.3</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -5652,13 +6197,13 @@
       <c r="B50" s="10" t="n">
         <v>3328193</v>
       </c>
-      <c r="C50" s="13" t="n">
+      <c r="C50" s="14" t="n">
         <v>1781.54</v>
       </c>
       <c r="D50" s="12" t="n">
         <v>0.1782</v>
       </c>
-      <c r="E50" s="14" t="n">
+      <c r="E50" s="15" t="n">
         <v>54.89</v>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -5679,13 +6224,13 @@
       <c r="B51" s="10" t="n">
         <v>3326820.44</v>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="14" t="n">
         <v>1716.9</v>
       </c>
       <c r="D51" s="12" t="n">
         <v>0.1717</v>
       </c>
-      <c r="E51" s="14" t="n">
+      <c r="E51" s="15" t="n">
         <v>53.66</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -5706,13 +6251,13 @@
       <c r="B52" s="10" t="n">
         <v>3321663.1</v>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="14" t="n">
         <v>1697.41</v>
       </c>
       <c r="D52" s="12" t="n">
         <v>0.1697</v>
       </c>
-      <c r="E52" s="14" t="n">
+      <c r="E52" s="15" t="n">
         <v>53.64</v>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -5733,13 +6278,13 @@
       <c r="B53" s="10" t="n">
         <v>3321562.67</v>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C53" s="14" t="n">
         <v>1683.71</v>
       </c>
       <c r="D53" s="12" t="n">
         <v>0.1684</v>
       </c>
-      <c r="E53" s="14" t="n">
+      <c r="E53" s="15" t="n">
         <v>53.31</v>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -5760,13 +6305,13 @@
       <c r="B54" s="10" t="n">
         <v>3366405.85</v>
       </c>
-      <c r="C54" s="13" t="n">
+      <c r="C54" s="14" t="n">
         <v>1677.43</v>
       </c>
       <c r="D54" s="12" t="n">
         <v>0.1677</v>
       </c>
-      <c r="E54" s="14" t="n">
+      <c r="E54" s="15" t="n">
         <v>53.35</v>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -5787,13 +6332,13 @@
       <c r="B55" s="10" t="n">
         <v>3404575.31</v>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C55" s="14" t="n">
         <v>1720.7</v>
       </c>
       <c r="D55" s="12" t="n">
         <v>0.1721</v>
       </c>
-      <c r="E55" s="14" t="n">
+      <c r="E55" s="15" t="n">
         <v>53.95</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -5814,13 +6359,13 @@
       <c r="B56" s="10" t="n">
         <v>3386087.66</v>
       </c>
-      <c r="C56" s="13" t="n">
+      <c r="C56" s="14" t="n">
         <v>1713.3</v>
       </c>
       <c r="D56" s="12" t="n">
         <v>0.1713</v>
       </c>
-      <c r="E56" s="14" t="n">
+      <c r="E56" s="15" t="n">
         <v>53.84</v>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -5841,13 +6386,13 @@
       <c r="B57" s="10" t="n">
         <v>3447826.41</v>
       </c>
-      <c r="C57" s="13" t="n">
+      <c r="C57" s="14" t="n">
         <v>1688.2</v>
       </c>
       <c r="D57" s="12" t="n">
         <v>0.1688</v>
       </c>
-      <c r="E57" s="14" t="n">
+      <c r="E57" s="15" t="n">
         <v>53.71</v>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -5868,13 +6413,13 @@
       <c r="B58" s="10" t="n">
         <v>3380957.39</v>
       </c>
-      <c r="C58" s="13" t="n">
+      <c r="C58" s="14" t="n">
         <v>1731.51</v>
       </c>
       <c r="D58" s="12" t="n">
         <v>0.1732</v>
       </c>
-      <c r="E58" s="14" t="n">
+      <c r="E58" s="15" t="n">
         <v>54.53</v>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -5895,13 +6440,13 @@
       <c r="B59" s="10" t="n">
         <v>3423735.61</v>
       </c>
-      <c r="C59" s="13" t="n">
+      <c r="C59" s="14" t="n">
         <v>1711.47</v>
       </c>
       <c r="D59" s="12" t="n">
         <v>0.1711</v>
       </c>
-      <c r="E59" s="14" t="n">
+      <c r="E59" s="15" t="n">
         <v>54.23</v>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -5922,13 +6467,13 @@
       <c r="B60" s="10" t="n">
         <v>3489700.37</v>
       </c>
-      <c r="C60" s="13" t="n">
+      <c r="C60" s="14" t="n">
         <v>1691.65</v>
       </c>
       <c r="D60" s="12" t="n">
         <v>0.1692</v>
       </c>
-      <c r="E60" s="14" t="n">
+      <c r="E60" s="15" t="n">
         <v>53.96</v>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -5949,13 +6494,13 @@
       <c r="B61" s="10" t="n">
         <v>3525507.31</v>
       </c>
-      <c r="C61" s="13" t="n">
+      <c r="C61" s="14" t="n">
         <v>1714.58</v>
       </c>
       <c r="D61" s="12" t="n">
         <v>0.1715</v>
       </c>
-      <c r="E61" s="14" t="n">
+      <c r="E61" s="15" t="n">
         <v>54.14</v>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -5976,13 +6521,13 @@
       <c r="B62" s="10" t="n">
         <v>3557468.59</v>
       </c>
-      <c r="C62" s="13" t="n">
+      <c r="C62" s="14" t="n">
         <v>1721.28</v>
       </c>
       <c r="D62" s="12" t="n">
         <v>0.1721</v>
       </c>
-      <c r="E62" s="14" t="n">
+      <c r="E62" s="15" t="n">
         <v>54.27</v>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -6003,13 +6548,13 @@
       <c r="B63" s="10" t="n">
         <v>3622549.69</v>
       </c>
-      <c r="C63" s="13" t="n">
+      <c r="C63" s="14" t="n">
         <v>1699.95</v>
       </c>
       <c r="D63" s="12" t="n">
         <v>0.17</v>
       </c>
-      <c r="E63" s="14" t="n">
+      <c r="E63" s="15" t="n">
         <v>54.03</v>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -6030,13 +6575,13 @@
       <c r="B64" s="10" t="n">
         <v>3614409.36</v>
       </c>
-      <c r="C64" s="13" t="n">
+      <c r="C64" s="14" t="n">
         <v>1682.42</v>
       </c>
       <c r="D64" s="12" t="n">
         <v>0.1682</v>
       </c>
-      <c r="E64" s="14" t="n">
+      <c r="E64" s="15" t="n">
         <v>53.79</v>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -6057,13 +6602,13 @@
       <c r="B65" s="10" t="n">
         <v>3645197.23</v>
       </c>
-      <c r="C65" s="13" t="n">
+      <c r="C65" s="14" t="n">
         <v>1669.26</v>
       </c>
       <c r="D65" s="12" t="n">
         <v>0.1669</v>
       </c>
-      <c r="E65" s="14" t="n">
+      <c r="E65" s="15" t="n">
         <v>53.55</v>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -6084,13 +6629,13 @@
       <c r="B66" s="10" t="n">
         <v>3682392.52</v>
       </c>
-      <c r="C66" s="13" t="n">
+      <c r="C66" s="14" t="n">
         <v>1667.2</v>
       </c>
       <c r="D66" s="12" t="n">
         <v>0.1667</v>
       </c>
-      <c r="E66" s="14" t="n">
+      <c r="E66" s="15" t="n">
         <v>53.43</v>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -6111,13 +6656,13 @@
       <c r="B67" s="10" t="n">
         <v>3686690.04</v>
       </c>
-      <c r="C67" s="13" t="n">
+      <c r="C67" s="14" t="n">
         <v>1699.04</v>
       </c>
       <c r="D67" s="12" t="n">
         <v>0.1699</v>
       </c>
-      <c r="E67" s="14" t="n">
+      <c r="E67" s="15" t="n">
         <v>53.8</v>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -6138,13 +6683,13 @@
       <c r="B68" s="10" t="n">
         <v>3736970.25</v>
       </c>
-      <c r="C68" s="13" t="n">
+      <c r="C68" s="14" t="n">
         <v>1698.27</v>
       </c>
       <c r="D68" s="12" t="n">
         <v>0.1698</v>
       </c>
-      <c r="E68" s="14" t="n">
+      <c r="E68" s="15" t="n">
         <v>53.8</v>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -6165,13 +6710,13 @@
       <c r="B69" s="10" t="n">
         <v>3762914</v>
       </c>
-      <c r="C69" s="13" t="n">
+      <c r="C69" s="14" t="n">
         <v>1662.76</v>
       </c>
       <c r="D69" s="12" t="n">
         <v>0.1663</v>
       </c>
-      <c r="E69" s="14" t="n">
+      <c r="E69" s="15" t="n">
         <v>53.6</v>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -6192,13 +6737,13 @@
       <c r="B70" s="10" t="n">
         <v>3757762.35</v>
       </c>
-      <c r="C70" s="13" t="n">
+      <c r="C70" s="14" t="n">
         <v>1632.55</v>
       </c>
       <c r="D70" s="12" t="n">
         <v>0.1633</v>
       </c>
-      <c r="E70" s="14" t="n">
+      <c r="E70" s="15" t="n">
         <v>53.9</v>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -6219,13 +6764,13 @@
       <c r="B71" s="10" t="n">
         <v>3790000.53</v>
       </c>
-      <c r="C71" s="13" t="n">
+      <c r="C71" s="14" t="n">
         <v>1620.92</v>
       </c>
       <c r="D71" s="12" t="n">
         <v>0.1621</v>
       </c>
-      <c r="E71" s="14" t="n">
+      <c r="E71" s="15" t="n">
         <v>53.25</v>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -6246,13 +6791,13 @@
       <c r="B72" s="10" t="n">
         <v>3837176.88</v>
       </c>
-      <c r="C72" s="13" t="n">
+      <c r="C72" s="14" t="n">
         <v>1589.84</v>
       </c>
       <c r="D72" s="12" t="n">
         <v>0.159</v>
       </c>
-      <c r="E72" s="14" t="n">
+      <c r="E72" s="15" t="n">
         <v>53.21</v>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -6273,13 +6818,13 @@
       <c r="B73" s="10" t="n">
         <v>3812249.89</v>
       </c>
-      <c r="C73" s="13" t="n">
+      <c r="C73" s="14" t="n">
         <v>1605.6</v>
       </c>
       <c r="D73" s="12" t="n">
         <v>0.1606</v>
       </c>
-      <c r="E73" s="14" t="n">
+      <c r="E73" s="15" t="n">
         <v>53.52</v>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -6300,13 +6845,13 @@
       <c r="B74" s="10" t="n">
         <v>3851151.56</v>
       </c>
-      <c r="C74" s="13" t="n">
+      <c r="C74" s="14" t="n">
         <v>1609.11</v>
       </c>
       <c r="D74" s="12" t="n">
         <v>0.1609</v>
       </c>
-      <c r="E74" s="14" t="n">
+      <c r="E74" s="15" t="n">
         <v>53.65</v>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -6327,13 +6872,13 @@
       <c r="B75" s="10" t="n">
         <v>3893504.01</v>
       </c>
-      <c r="C75" s="13" t="n">
+      <c r="C75" s="14" t="n">
         <v>1591.23</v>
       </c>
       <c r="D75" s="12" t="n">
         <v>0.1591</v>
       </c>
-      <c r="E75" s="14" t="n">
+      <c r="E75" s="15" t="n">
         <v>53.49</v>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -6354,13 +6899,13 @@
       <c r="B76" s="10" t="n">
         <v>3913968.89</v>
       </c>
-      <c r="C76" s="13" t="n">
+      <c r="C76" s="14" t="n">
         <v>1571.47</v>
       </c>
       <c r="D76" s="12" t="n">
         <v>0.1571</v>
       </c>
-      <c r="E76" s="14" t="n">
+      <c r="E76" s="15" t="n">
         <v>52.96</v>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -6381,13 +6926,13 @@
       <c r="B77" s="10" t="n">
         <v>3916782.68</v>
       </c>
-      <c r="C77" s="13" t="n">
+      <c r="C77" s="14" t="n">
         <v>1563.58</v>
       </c>
       <c r="D77" s="12" t="n">
         <v>0.1564</v>
       </c>
-      <c r="E77" s="14" t="n">
+      <c r="E77" s="15" t="n">
         <v>52.66</v>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -6408,13 +6953,13 @@
       <c r="B78" s="10" t="n">
         <v>3985659.55</v>
       </c>
-      <c r="C78" s="13" t="n">
+      <c r="C78" s="14" t="n">
         <v>1566.29</v>
       </c>
       <c r="D78" s="12" t="n">
         <v>0.1566</v>
       </c>
-      <c r="E78" s="14" t="n">
+      <c r="E78" s="15" t="n">
         <v>52.66</v>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -6435,13 +6980,13 @@
       <c r="B79" s="10" t="n">
         <v>3943926.9</v>
       </c>
-      <c r="C79" s="13" t="n">
+      <c r="C79" s="14" t="n">
         <v>1571.34</v>
       </c>
       <c r="D79" s="12" t="n">
         <v>0.1571</v>
       </c>
-      <c r="E79" s="14" t="n">
+      <c r="E79" s="15" t="n">
         <v>52.58</v>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -6462,13 +7007,13 @@
       <c r="B80" s="10" t="n">
         <v>3933611.94</v>
       </c>
-      <c r="C80" s="13" t="n">
+      <c r="C80" s="14" t="n">
         <v>1569.6</v>
       </c>
       <c r="D80" s="12" t="n">
         <v>0.157</v>
       </c>
-      <c r="E80" s="14" t="n">
+      <c r="E80" s="15" t="n">
         <v>52.59</v>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -6489,13 +7034,13 @@
       <c r="B81" s="10" t="n">
         <v>4001401.41</v>
       </c>
-      <c r="C81" s="13" t="n">
+      <c r="C81" s="14" t="n">
         <v>1558.11</v>
       </c>
       <c r="D81" s="12" t="n">
         <v>0.1558</v>
       </c>
-      <c r="E81" s="14" t="n">
+      <c r="E81" s="15" t="n">
         <v>52.35</v>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -6516,13 +7061,13 @@
       <c r="B82" s="10" t="n">
         <v>4002277.04</v>
       </c>
-      <c r="C82" s="13" t="n">
+      <c r="C82" s="14" t="n">
         <v>1570.32</v>
       </c>
       <c r="D82" s="12" t="n">
         <v>0.157</v>
       </c>
-      <c r="E82" s="14" t="n">
+      <c r="E82" s="15" t="n">
         <v>52.66</v>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -6543,13 +7088,13 @@
       <c r="B83" s="10" t="n">
         <v>4055963</v>
       </c>
-      <c r="C83" s="13" t="n">
+      <c r="C83" s="14" t="n">
         <v>1554.51</v>
       </c>
       <c r="D83" s="12" t="n">
         <v>0.1555</v>
       </c>
-      <c r="E83" s="14" t="n">
+      <c r="E83" s="15" t="n">
         <v>52.4</v>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -6570,13 +7115,13 @@
       <c r="B84" s="10" t="n">
         <v>4136176</v>
       </c>
-      <c r="C84" s="13" t="n">
+      <c r="C84" s="14" t="n">
         <v>1537.62</v>
       </c>
       <c r="D84" s="12" t="n">
         <v>0.1538</v>
       </c>
-      <c r="E84" s="14" t="n">
+      <c r="E84" s="15" t="n">
         <v>52.08</v>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -6597,13 +7142,13 @@
       <c r="B85" s="10" t="n">
         <v>4192699</v>
       </c>
-      <c r="C85" s="13" t="n">
+      <c r="C85" s="14" t="n">
         <v>1513.42</v>
       </c>
       <c r="D85" s="12" t="n">
         <v>0.1513</v>
       </c>
-      <c r="E85" s="14" t="n">
+      <c r="E85" s="15" t="n">
         <v>52.38</v>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -6624,13 +7169,13 @@
       <c r="B86" s="10" t="n">
         <v>4219434</v>
       </c>
-      <c r="C86" s="13" t="n">
+      <c r="C86" s="14" t="n">
         <v>1515.68</v>
       </c>
       <c r="D86" s="12" t="n">
         <v>0.1516</v>
       </c>
-      <c r="E86" s="14" t="n">
+      <c r="E86" s="15" t="n">
         <v>52.47</v>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6651,13 +7196,13 @@
       <c r="B87" s="10" t="n">
         <v>4390875</v>
       </c>
-      <c r="C87" s="13" t="n">
+      <c r="C87" s="14" t="n">
         <v>1492.36</v>
       </c>
       <c r="D87" s="12" t="n">
         <v>0.1492</v>
       </c>
-      <c r="E87" s="14" t="n">
+      <c r="E87" s="15" t="n">
         <v>51.5</v>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -6678,13 +7223,13 @@
       <c r="B88" s="10" t="n">
         <v>4388307</v>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C88" s="14" t="n">
         <v>1474.22</v>
       </c>
       <c r="D88" s="12" t="n">
         <v>0.1474</v>
       </c>
-      <c r="E88" s="14" t="n">
+      <c r="E88" s="15" t="n">
         <v>51.25</v>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -6705,13 +7250,13 @@
       <c r="B89" s="10" t="n">
         <v>4447192</v>
       </c>
-      <c r="C89" s="13" t="n">
+      <c r="C89" s="14" t="n">
         <v>1471.17</v>
       </c>
       <c r="D89" s="12" t="n">
         <v>0.1471</v>
       </c>
-      <c r="E89" s="14" t="n">
+      <c r="E89" s="15" t="n">
         <v>51.16</v>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -6732,13 +7277,13 @@
       <c r="B90" s="10" t="n">
         <v>4584304.35</v>
       </c>
-      <c r="C90" s="13" t="n">
+      <c r="C90" s="14" t="n">
         <v>1474.45</v>
       </c>
       <c r="D90" s="12" t="n">
         <v>0.1474</v>
       </c>
-      <c r="E90" s="14" t="n">
+      <c r="E90" s="15" t="n">
         <v>51.51</v>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -6759,13 +7304,13 @@
       <c r="B91" s="10" t="n">
         <v>4537731</v>
       </c>
-      <c r="C91" s="13" t="n">
+      <c r="C91" s="14" t="n">
         <v>1491.98</v>
       </c>
       <c r="D91" s="12" t="n">
         <v>0.1492</v>
       </c>
-      <c r="E91" s="14" t="n">
+      <c r="E91" s="15" t="n">
         <v>51.63</v>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -6786,13 +7331,13 @@
       <c r="B92" s="10" t="n">
         <v>4623904</v>
       </c>
-      <c r="C92" s="13" t="n">
+      <c r="C92" s="14" t="n">
         <v>1476.92</v>
       </c>
       <c r="D92" s="12" t="n">
         <v>0.1477</v>
       </c>
-      <c r="E92" s="14" t="n">
+      <c r="E92" s="15" t="n">
         <v>51.42</v>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -6813,13 +7358,13 @@
       <c r="B93" s="10" t="n">
         <v>4771512.84</v>
       </c>
-      <c r="C93" s="13" t="n">
+      <c r="C93" s="14" t="n">
         <v>1431.3</v>
       </c>
       <c r="D93" s="12" t="n">
         <v>0.1431</v>
       </c>
-      <c r="E93" s="14" t="n">
+      <c r="E93" s="15" t="n">
         <v>50.72</v>
       </c>
       <c r="F93" s="6" t="inlineStr">
